--- a/Handoff/DeviceIdentifier-API-Reference.xlsx
+++ b/Handoff/DeviceIdentifier-API-Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\Handoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C290BCA-6CA3-4C86-BE00-467E7AEEEFD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F14E3B-5519-41A4-B60E-8582698188E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,8 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Detail!$A$4:$F$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Reference'!$A$4:$C$57</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Quick Reference'!$A$4:$C$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Full Reference'!$A$4:$C$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Quick Reference'!$A$4:$C$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="311">
   <si>
     <t>DeviceIdentifier — API</t>
   </si>
@@ -60,6 +60,41 @@
     <t>What it does</t>
   </si>
   <si>
+    <t>Entry point — the call you write</t>
+  </si>
+  <si>
+    <t>1. Construct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">var sqlReader = new PythonSQL(connectionString);
+IPredictionClient client = new HttpPredictionClient(mlServiceUrl);
+var logic     = new LogicAssignment(connectionString);
+</t>
+  </si>
+  <si>
+    <t>2. Run the pipeline</t>
+  </si>
+  <si>
+    <t>var result = await DevicePipeline.RunAsync(
+    sqlReader:      sqlReader,
+    client:         client,
+    logic:          logic,
+    sqlSourceTable: "dbo.DummyTestingData",
+    sqlQuotaTable:  "dbo.PatternCluster",
+    sqlOutputDir:   @"...\data",
+    projectCode:    "A9998",
+    callbacks:      null);</t>
+  </si>
+  <si>
+    <t>3. Read the result</t>
+  </si>
+  <si>
+    <t>foreach (var group in result.ClusterGroups)
+{
+    // group.Section, group.Cluster, group.Devices
+}</t>
+  </si>
+  <si>
     <t>Entry point — DevicePipeline.RunAsync</t>
   </si>
   <si>
@@ -397,6 +432,15 @@
   </si>
   <si>
     <t>The one-page cheat sheet. Environment setup is on the Detail sheet.</t>
+  </si>
+  <si>
+    <t>var result = await DevicePipeline.RunAsync(
+    sqlReader, client, logic,
+    "dbo.DummyTestingData",   // source table
+    "dbo.PatternCluster",     // quota table
+    @"...\data",             // scratch folder
+    "A9998",                  // project code
+    callbacks: null);         // optional progress hooks</t>
   </si>
   <si>
     <t>What you get back (DevicePipelineResult)</t>
@@ -955,7 +999,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1014,8 +1058,29 @@
       <color rgb="FF9AA5B1"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF1F3864"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.5"/>
+      <color rgb="FF1F2933"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF1F2933"/>
+      <name val="Consolas"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF9AA5B1"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1032,8 +1097,13 @@
         <fgColor rgb="FFDCE6F1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1050,11 +1120,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB8C4D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1086,6 +1165,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1389,7 +1486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1397,7 +1494,7 @@
     <col min="3" max="3" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1508,7 @@
       </c>
       <c r="C2" s="4">
         <f>COUNTA(B5:B2000)</f>
-        <v>53</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -1425,108 +1522,108 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="16" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="19" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
+    <row r="7" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="19" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="10" t="s">
+      <c r="A8" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="B8" s="7" t="s">
         <v>14</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="7" t="s">
+      <c r="A13" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C13" s="8" t="s">
+      <c r="C13" s="11" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>26</v>
@@ -1537,7 +1634,7 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>28</v>
@@ -1547,85 +1644,85 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B16" s="10" t="s">
+      <c r="A16" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="B16" s="7" t="s">
         <v>31</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B22" s="7" t="s">
+      <c r="A22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="11" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>45</v>
@@ -1636,7 +1733,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>47</v>
@@ -1646,63 +1743,63 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B25" s="10" t="s">
+      <c r="A25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="B25" s="7" t="s">
         <v>50</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="7" t="s">
+      <c r="A29" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B29" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="C29" s="8" t="s">
+      <c r="C29" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>60</v>
@@ -1713,7 +1810,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>62</v>
@@ -1723,52 +1820,52 @@
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="10" t="s">
+      <c r="A32" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C32" s="11" t="s">
+      <c r="B32" s="7" t="s">
         <v>65</v>
+      </c>
+      <c r="C32" s="8" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A35" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="7" t="s">
+      <c r="A35" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="B35" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C35" s="8" t="s">
+      <c r="C35" s="11" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>73</v>
@@ -1779,7 +1876,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="B37" s="10" t="s">
         <v>75</v>
@@ -1789,63 +1886,63 @@
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A38" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="10" t="s">
+      <c r="A38" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="B38" s="7" t="s">
         <v>78</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A42" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B42" s="7" t="s">
+      <c r="A42" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="B42" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C42" s="8" t="s">
+      <c r="C42" s="11" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>88</v>
@@ -1856,7 +1953,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>90</v>
@@ -1866,157 +1963,190 @@
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" s="10" t="s">
+      <c r="A45" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C45" s="11" t="s">
+      <c r="B45" s="7" t="s">
         <v>93</v>
+      </c>
+      <c r="C45" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="B48" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>87</v>
+      <c r="A48" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A51" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="B51" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>104</v>
+      <c r="A51" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A53" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C52" s="11" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A53" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="8" t="s">
+      <c r="B53" s="10" t="s">
         <v>108</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="10" t="s">
+      <c r="A56" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="C56" s="11" t="s">
+      <c r="B56" s="7" t="s">
         <v>114</v>
+      </c>
+      <c r="C56" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C57" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:C60" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C49"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -2024,21 +2154,21 @@
     <col min="3" max="3" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C2" s="4">
         <f>COUNTA(B5:B2000)</f>
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="20" customHeight="1" x14ac:dyDescent="0.35">
@@ -2052,400 +2182,400 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A6" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A7" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="11" t="s">
-        <v>122</v>
+    <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A8" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>123</v>
+      <c r="A8" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A14" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>114</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>130</v>
+      <c r="A14" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>134</v>
+      <c r="A16" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>136</v>
+      <c r="A17" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
-        <v>132</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>139</v>
-      </c>
-      <c r="C19" s="11" t="s">
+      <c r="A19" s="6" t="s">
         <v>140</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="C25" s="8" t="s">
+      <c r="A25" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>153</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>158</v>
-      </c>
-      <c r="C28" s="11" t="s">
+      <c r="A28" s="6" t="s">
         <v>159</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>62</v>
+        <v>168</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A34" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B34" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="8" t="s">
-        <v>170</v>
+      <c r="A34" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A37" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>174</v>
+      <c r="A37" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>55</v>
+        <v>180</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="B40" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>108</v>
+      <c r="B40" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
@@ -2453,10 +2583,10 @@
         <v>177</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>111</v>
+        <v>60</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>112</v>
+        <v>183</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
@@ -2464,91 +2594,124 @@
         <v>177</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>109</v>
+        <v>62</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>110</v>
+        <v>184</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A43" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="B43" s="10" t="s">
-        <v>113</v>
-      </c>
-      <c r="C43" s="11" t="s">
+      <c r="A43" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B43" s="7" t="s">
         <v>114</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C44" s="11" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A45" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="B45" s="10" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A45" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B45" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>180</v>
+      <c r="C45" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>182</v>
+        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>183</v>
+        <v>122</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>184</v>
+        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A48" s="9" t="s">
-        <v>178</v>
-      </c>
-      <c r="B48" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="C48" s="11" t="s">
+      <c r="A48" s="6" t="s">
         <v>186</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="C48" s="8" t="s">
+        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A50" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A51" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A52" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="B52" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>196</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:C49" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A4:C52" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2566,14 +2729,14 @@
     <col min="6" max="6" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="18" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
@@ -2585,881 +2748,881 @@
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="F7" s="11" t="s">
         <v>207</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="37.5" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="F14" s="11"/>
     </row>
-    <row r="15" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="F21" s="11" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F22" s="11" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B24" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C24" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="F24" s="11"/>
     </row>
-    <row r="25" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="F33" s="11"/>
     </row>
-    <row r="34" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="F36" s="11"/>
     </row>
-    <row r="37" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B40" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B41" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="F41" s="11"/>
     </row>
-    <row r="42" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B43" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C43" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B44" s="13" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="C44" s="13" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="F44" s="11"/>
     </row>
-    <row r="45" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="F45" s="11"/>
     </row>
-    <row r="46" spans="1:6" ht="25" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="7" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="10" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="10" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="10" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="10" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="F51" s="11"/>
     </row>

--- a/Handoff/DeviceIdentifier-API-Reference.xlsx
+++ b/Handoff/DeviceIdentifier-API-Reference.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sitisyaziyah\source\repos\DeviceCluster\Handoff\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F14E3B-5519-41A4-B60E-8582698188E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7B3882-6314-4D3C-917C-DC9E1DE93DA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="312">
   <si>
     <t>DeviceIdentifier — API</t>
   </si>
@@ -58,9 +58,6 @@
   </si>
   <si>
     <t>What it does</t>
-  </si>
-  <si>
-    <t>Entry point — the call you write</t>
   </si>
   <si>
     <t>1. Construct</t>
@@ -994,12 +991,18 @@
   <si>
     <t>python/ folder structure — scripts find models by relative path</t>
   </si>
+  <si>
+    <t xml:space="preserve">Entry point </t>
+  </si>
+  <si>
+    <t>Entry point</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1059,12 +1062,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF1F3864"/>
-      <name val="Arial"/>
-    </font>
-    <font>
       <sz val="9.5"/>
       <color rgb="FF1F2933"/>
       <name val="Consolas"/>
@@ -1073,11 +1070,6 @@
       <sz val="9"/>
       <color rgb="FF1F2933"/>
       <name val="Consolas"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF9AA5B1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1166,22 +1158,22 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1523,619 +1515,619 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="135" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="19" t="s">
+    </row>
+    <row r="7" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="16" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B9" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C9" s="11" t="s">
         <v>16</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B10" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="11" t="s">
         <v>18</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="11" t="s">
         <v>20</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="11" t="s">
         <v>22</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>24</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C14" s="11" t="s">
         <v>26</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="11" t="s">
         <v>28</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>31</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>35</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B19" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>39</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>41</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>45</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>47</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B25" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="C25" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="C28" s="11" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B32" s="7" t="s">
+      <c r="C32" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>67</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>69</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B35" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="11" t="s">
         <v>71</v>
-      </c>
-      <c r="C35" s="11" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="11" t="s">
         <v>75</v>
-      </c>
-      <c r="C37" s="11" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="B38" s="7" t="s">
+      <c r="C38" s="8" t="s">
         <v>78</v>
-      </c>
-      <c r="C38" s="8" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B39" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B40" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C40" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="C40" s="11" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B41" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="C42" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="C42" s="11" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B43" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="11" t="s">
         <v>88</v>
-      </c>
-      <c r="C43" s="11" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B44" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>90</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="C45" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="C47" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B48" s="10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C48" s="11" t="s">
         <v>99</v>
-      </c>
-      <c r="C48" s="11" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="11" t="s">
         <v>101</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="C51" s="8" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="C52" s="11" t="s">
         <v>106</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="C53" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="C53" s="11" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="C54" s="11" t="s">
         <v>110</v>
-      </c>
-      <c r="C54" s="11" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" s="9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B56" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="7" t="s">
+      <c r="C56" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="C56" s="8" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B57" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C57" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C57" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B58" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C58" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="C58" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B59" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C59" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="C59" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B60" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C60" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="C60" s="11" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2156,12 +2148,12 @@
   <sheetData>
     <row r="1" spans="1:3" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>2</v>
@@ -2183,531 +2175,531 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="18" t="s">
+        <v>310</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="C5" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="16" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="B6" s="16" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="105" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>126</v>
+      <c r="C6" s="17" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="s">
+      <c r="A7" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="17" t="s">
         <v>11</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>127</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>137</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>121</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="B19" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="C19" s="8" t="s">
         <v>141</v>
-      </c>
-      <c r="C19" s="8" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B20" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B21" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="C21" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B22" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>149</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B24" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="C24" s="11" t="s">
         <v>151</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B25" s="10" t="s">
+        <v>152</v>
+      </c>
+      <c r="C25" s="11" t="s">
         <v>153</v>
-      </c>
-      <c r="C25" s="11" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B26" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>155</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="C27" s="11" t="s">
         <v>157</v>
-      </c>
-      <c r="C27" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B28" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C28" s="8" t="s">
         <v>160</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="C29" s="11" t="s">
         <v>162</v>
-      </c>
-      <c r="C29" s="11" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B30" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="C30" s="11" t="s">
         <v>164</v>
-      </c>
-      <c r="C30" s="11" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B31" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="C31" s="11" t="s">
         <v>166</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B32" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>168</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B33" s="10" t="s">
+        <v>169</v>
+      </c>
+      <c r="C33" s="11" t="s">
         <v>170</v>
-      </c>
-      <c r="C33" s="11" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B34" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>172</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B36" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="C36" s="11" t="s">
         <v>175</v>
-      </c>
-      <c r="C36" s="11" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C37" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="C37" s="8" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B39" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C39" s="11" t="s">
         <v>180</v>
-      </c>
-      <c r="C39" s="11" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B43" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>114</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B44" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" s="11" t="s">
         <v>118</v>
-      </c>
-      <c r="C44" s="11" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B45" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="11" t="s">
         <v>116</v>
-      </c>
-      <c r="C45" s="11" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B46" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="C46" s="11" t="s">
         <v>120</v>
-      </c>
-      <c r="C46" s="11" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" s="9" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B47" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="C47" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="C47" s="11" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="B48" s="7" t="s">
+      <c r="C48" s="8" t="s">
         <v>187</v>
-      </c>
-      <c r="C48" s="8" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B49" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="C49" s="11" t="s">
         <v>189</v>
-      </c>
-      <c r="C49" s="11" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B50" s="10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C50" s="11" t="s">
         <v>191</v>
-      </c>
-      <c r="C50" s="11" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B51" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="C51" s="11" t="s">
         <v>193</v>
-      </c>
-      <c r="C51" s="11" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" s="9" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B52" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" s="11" t="s">
         <v>195</v>
-      </c>
-      <c r="C52" s="11" t="s">
-        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2731,12 +2723,12 @@
   <sheetData>
     <row r="1" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>2</v>
@@ -2748,881 +2740,881 @@
     </row>
     <row r="4" spans="1:6" ht="20" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="C5" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="E5" s="8" t="s">
         <v>207</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="F5" s="8" t="s">
         <v>208</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C6" s="13" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>206</v>
-      </c>
       <c r="D6" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>210</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="F6" s="11" t="s">
         <v>211</v>
-      </c>
-      <c r="F6" s="11" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C7" s="13" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="E7" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="E7" s="11" t="s">
-        <v>215</v>
-      </c>
       <c r="F7" s="11" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C8" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D8" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="E8" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="E8" s="11" t="s">
+      <c r="F8" s="11" t="s">
         <v>217</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B9" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C9" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D9" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="E9" s="11" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="11" t="s">
-        <v>220</v>
-      </c>
       <c r="F9" s="11" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C10" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D10" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="E10" s="11" t="s">
-        <v>222</v>
-      </c>
       <c r="F10" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B11" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C11" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D11" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="E11" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>224</v>
-      </c>
       <c r="F11" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B12" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C12" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D12" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="E12" s="11" t="s">
-        <v>226</v>
-      </c>
       <c r="F12" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>204</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>205</v>
-      </c>
       <c r="C13" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D13" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="E13" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="E13" s="11" t="s">
-        <v>228</v>
-      </c>
       <c r="F13" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B14" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C14" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="D14" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="11" t="s">
         <v>231</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>232</v>
       </c>
       <c r="F14" s="11"/>
     </row>
     <row r="15" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B15" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C15" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>230</v>
-      </c>
       <c r="D15" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E15" s="11" t="s">
         <v>233</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>234</v>
       </c>
       <c r="F15" s="11"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B16" s="13" t="s">
+        <v>228</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>230</v>
-      </c>
       <c r="D16" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>235</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>236</v>
       </c>
       <c r="F16" s="11"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C17" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="11" t="s">
         <v>238</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>239</v>
       </c>
       <c r="F17" s="11"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D18" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="E18" s="11" t="s">
         <v>240</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>241</v>
       </c>
       <c r="F18" s="11"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D19" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="11" t="s">
         <v>242</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>243</v>
       </c>
       <c r="F19" s="11"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D20" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="E20" s="11" t="s">
         <v>244</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>245</v>
       </c>
       <c r="F20" s="11"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C21" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="D21" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="E21" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F21" s="11" t="s">
         <v>247</v>
-      </c>
-      <c r="E21" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D22" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="11" t="s">
         <v>249</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D23" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>251</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B24" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C24" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="D24" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>254</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>255</v>
       </c>
       <c r="F24" s="11"/>
     </row>
     <row r="25" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B25" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D25" s="10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="F25" s="11"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B26" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C26" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D26" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F26" s="11"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B27" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C27" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D27" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="F27" s="11"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B28" s="13" t="s">
+        <v>252</v>
+      </c>
+      <c r="C28" s="13" t="s">
         <v>253</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>254</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F28" s="11"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C29" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="D29" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="E29" s="11" t="s">
         <v>261</v>
-      </c>
-      <c r="E29" s="11" t="s">
-        <v>262</v>
       </c>
       <c r="F29" s="11"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B30" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C30" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D30" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" s="11" t="s">
         <v>263</v>
-      </c>
-      <c r="E30" s="11" t="s">
-        <v>264</v>
       </c>
       <c r="F30" s="11"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D31" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E31" s="11" t="s">
         <v>265</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>266</v>
       </c>
       <c r="F31" s="11"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D32" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="E32" s="11" t="s">
         <v>267</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>268</v>
       </c>
       <c r="F32" s="11"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B33" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D33" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="E33" s="11" t="s">
         <v>269</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>270</v>
       </c>
       <c r="F33" s="11"/>
     </row>
     <row r="34" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B34" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D34" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="E34" s="11" t="s">
         <v>271</v>
-      </c>
-      <c r="E34" s="11" t="s">
-        <v>272</v>
       </c>
       <c r="F34" s="11"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B35" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="F35" s="11"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D36" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="E36" s="11" t="s">
         <v>274</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>275</v>
       </c>
       <c r="F36" s="11"/>
     </row>
     <row r="37" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B37" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D37" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="E37" s="11" t="s">
         <v>276</v>
-      </c>
-      <c r="E37" s="11" t="s">
-        <v>277</v>
       </c>
       <c r="F37" s="11"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B38" s="13" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D38" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="E38" s="11" t="s">
         <v>278</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>279</v>
       </c>
       <c r="F38" s="11"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B39" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C39" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C39" s="13" t="s">
+      <c r="D39" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="E39" s="11" t="s">
         <v>282</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>283</v>
       </c>
       <c r="F39" s="11"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B40" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C40" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D40" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="E40" s="11" t="s">
         <v>284</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="F40" s="11"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B41" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C41" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D41" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="E41" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>287</v>
       </c>
       <c r="F41" s="11"/>
     </row>
     <row r="42" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B42" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C42" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D42" s="10" t="s">
+        <v>287</v>
+      </c>
+      <c r="E42" s="11" t="s">
         <v>288</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="F42" s="11"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B43" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C43" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C43" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D43" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="E43" s="11" t="s">
         <v>290</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>291</v>
       </c>
       <c r="F43" s="11"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B44" s="13" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="13" t="s">
         <v>280</v>
       </c>
-      <c r="C44" s="13" t="s">
-        <v>281</v>
-      </c>
       <c r="D44" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="E44" s="11" t="s">
         <v>292</v>
-      </c>
-      <c r="E44" s="11" t="s">
-        <v>293</v>
       </c>
       <c r="F44" s="11"/>
     </row>
     <row r="45" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B45" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C45" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="D45" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="E45" s="11" t="s">
         <v>296</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>297</v>
       </c>
       <c r="F45" s="11"/>
     </row>
     <row r="46" spans="1:6" ht="25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B46" s="13" t="s">
+        <v>293</v>
+      </c>
+      <c r="C46" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="C46" s="13" t="s">
-        <v>295</v>
-      </c>
       <c r="D46" s="10" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F46" s="11"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>299</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>300</v>
       </c>
       <c r="C47" s="12"/>
       <c r="D47" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E47" s="8" t="s">
         <v>301</v>
-      </c>
-      <c r="E47" s="8" t="s">
-        <v>302</v>
       </c>
       <c r="F47" s="8"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B48" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>300</v>
       </c>
       <c r="C48" s="13"/>
       <c r="D48" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="E48" s="11" t="s">
         <v>303</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>304</v>
       </c>
       <c r="F48" s="11"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B49" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>300</v>
       </c>
       <c r="C49" s="13"/>
       <c r="D49" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="E49" s="11" t="s">
         <v>305</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>306</v>
       </c>
       <c r="F49" s="11"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B50" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>300</v>
       </c>
       <c r="C50" s="13"/>
       <c r="D50" s="10" t="s">
+        <v>306</v>
+      </c>
+      <c r="E50" s="11" t="s">
         <v>307</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>308</v>
       </c>
       <c r="F50" s="11"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="9" t="s">
+        <v>298</v>
+      </c>
+      <c r="B51" s="13" t="s">
         <v>299</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>300</v>
       </c>
       <c r="C51" s="13"/>
       <c r="D51" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="E51" s="11" t="s">
         <v>309</v>
-      </c>
-      <c r="E51" s="11" t="s">
-        <v>310</v>
       </c>
       <c r="F51" s="11"/>
     </row>
